--- a/data/vendor-search/results_all_fridge.xlsx
+++ b/data/vendor-search/results_all_fridge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -475,8 +480,10 @@
       <c r="D2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E2" t="n">
-        <v>3.1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -486,6 +493,11 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>cpe:2.3:o:mitsubishielectric:mac-557if-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-557if-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-557if-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-557if-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:pac-wf010-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:pac-wf010-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-566ifb-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-566ifb-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-576if-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-576if-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-567ifb-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-567ifb-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-567ifb2-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-567ifb2-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-558if-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-558if-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-558if-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-558if-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-559if-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-559if-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-559if-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-559if-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-568if-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-568if-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-568ifb-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-568ifb-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-568ifb2-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-568ifb2-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-568ifb3-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-568ifb3-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:pac-whs01wf-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:pac-whs01wf-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:s-mac-702if-f_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:s-mac-702if-f:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:s-mac-702if-z_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:s-mac-702if-z:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:s-mac-702if-b_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:s-mac-702if-b:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:s-mac-905if_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:s-mac-905if:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:s-mac-906if_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:s-mac-906if:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap60\/71vgk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap60\/71vgk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap60\/71vgk-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap60\/71vgk-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap60\/71vgk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap60\/71vgk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e6:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vgw-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vgw-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vgv-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vgv-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vgb-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vgb-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vgr-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vgr-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vgw-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vgw-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vgv-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vgv-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vgb-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vgb-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vgr-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vgr-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50vg2w-en1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50vg2w-en1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50vg2v-en1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50vg2v-en1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50vg2b-en1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50vg2b-en1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50vg2r-en1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50vg2r-en1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vgv-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vgv-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vgb-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vgb-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vgr-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vgr-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft20\/25vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft20\/25vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-fx20\/25vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-fx20\/25vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-gzt09\/12\/18vak_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-gzt09\/12\/18vak:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-zt09\/12\/18vak_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-zt09\/12\/18vak:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-587if-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-587if-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-587if2-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-587if2-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-507if-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-507if-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-588if-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-588if-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:s-mac-002if_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:s-mac-002if:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:ma-ew85s-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:ma-ew85s-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:ma-ew85s-uk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:ma-ew85s-uk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msxy-fp05\/07\/10\/13\/18\/20\/24vgk-sg1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msxy-fp05\/07\/10\/13\/18\/20\/24vgk-sg1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msy-gp10\/13\/15\/18\/20\/24vfk-sg1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msy-gp10\/13\/15\/18\/20\/24vfk-sg1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e7_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e7:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e8_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e8:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-er3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-er3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgk-e6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgk-e6:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgk-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgk-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgk-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgk-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-e6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-e6:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkw-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkw-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkb-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkb-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgks-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgks-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkw-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkw-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkb-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkb-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgks-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgks-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft25\/35\/50vgk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft25\/35\/50vgk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft25\/35\/50vgk-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft25\/35\/50vgk-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft25\/35\/50vgk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft25\/35\/50vgk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft25\/35\/50vgk-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft25\/35\/50vgk-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft25\/35\/50vgk-sc2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft25\/35\/50vgk-sc2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-hr25\/35\/42\/50vfk-e6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-hr25\/35\/42\/50vfk-e6:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2w-en2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2w-en2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2w-er3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2w-er3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2w-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2w-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2v-en2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2v-en2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-er3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-er3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2b-en2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2b-en2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-er3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-er3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2r-en2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2r-en2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-er3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-er3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50vg2w-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50vg2w-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2v-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2v-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2b-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2b-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2r-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2r-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-rw25\/35\/50vg-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-rw25\/35\/50vg-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-rw25\/35\/50vg-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-rw25\/35\/50vg-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-rw25\/35\/50vg-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-rw25\/35\/50vg-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-rw25\/35\/50vg-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-rw25\/35\/50vg-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap22\/25\/35\/42\/50\/61\/70\/80vgkd-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap22\/25\/35\/42\/50\/61\/70\/80vgkd-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap22\/25\/35\/42\/50\/60\/71\/80vgkd-a2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap22\/25\/35\/42\/50\/60\/71\/80vgkd-a2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-a2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-a2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-a2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-a2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-a2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-a2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mfz-gxt50\/60\/73vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mfz-gxt50\/60\/73vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mfz-xt50\/60vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mfz-xt50\/60vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-eza09\/12vak_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-eza09\/12vak:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-exa09\/12vak_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-exa09\/12vak:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-gzy09\/12\/18vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-gzy09\/12\/18vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ky09\/12\/18vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ky09\/12\/18vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-wx18\/20\/25vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-wx18\/20\/25vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-zy09\/12\/18vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-zy09\/12\/18vfk:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
         </is>
       </c>
     </row>
@@ -509,8 +521,10 @@
       <c r="D3" t="n">
         <v>6.1</v>
       </c>
-      <c r="E3" t="n">
-        <v>3.1</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -520,6 +534,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>cpe:2.3:o:mitsubishielectric:mac-587if-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-587if-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-587if2-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-587if2-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-507if-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-507if-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mac-588if-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mac-588if-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:s-mac-002if_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:s-mac-002if:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:ma-ew85s-e_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:ma-ew85s-e:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:ma-ew85s-uk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:ma-ew85s-uk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mfz-gxt50\/60\/73vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mfz-gxt50\/60\/73vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:mfz-xt50\/60vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:mfz-xt50\/60vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msxy-fp05\/07\/10\/13\/18\/20\/24vgk-sg1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msxy-fp05\/07\/10\/13\/18\/20\/24vgk-sg1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msy-gp10\/13\/15\/18\/20\/24vfk-sg1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msy-gp10\/13\/15\/18\/20\/24vfk-sg1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap15\/20\/25\/35\/42\/50\/60\/71vgk-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap22\/25\/35\/42\/50\/60\/71\/80vgkd-a2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap22\/25\/35\/42\/50\/60\/71\/80vgkd-a2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap22\/25\/35\/42\/50\/61\/70\/80vgkd-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap22\/25\/35\/42\/50\/61\/70\/80vgkd-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-er3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-er3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50\/60\/71vgk-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e7_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e7:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e8_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-e8:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-en3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ap25\/35\/42\/50vgk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ap25\/35\/42\/50vgk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgk-e6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgk-e6:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgk-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgk-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgk-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgk-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-e6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-e6:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ay25\/35\/42\/50vgkp-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-bt20\/25\/35\/50vgk-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkb-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkb-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkb-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkb-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgks-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgks-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgks-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgks-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkw-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkw-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkw-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef18\/22\/25\/35\/42\/50vgkw-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkb-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgks-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-a1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-a1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ef22\/25\/35\/42\/50vgkw-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-exa09\/12vak_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-exa09\/12vak:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-eza09\/12vak_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-eza09\/12vak:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft25\/35\/50vgk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft25\/35\/50vgk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft25\/35\/50vgk-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft25\/35\/50vgk-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft25\/35\/50vgk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft25\/35\/50vgk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft25\/35\/50vgk-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft25\/35\/50vgk-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ft25\/35\/50vgk-sc2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ft25\/35\/50vgk-sc2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-gzy09\/12\/18vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-gzy09\/12\/18vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-hr25\/35\/42\/50\/60\/71vfk-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-hr25\/35\/42\/50vfk-e6_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-hr25\/35\/42\/50vfk-e6:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ky09\/12\/18vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ky09\/12\/18vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2b-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2r-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2v-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-e2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-e2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-e3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-e3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50\/60vg2w-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln18\/25\/35\/50vg2w-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln18\/25\/35\/50vg2w-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-a2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-a2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-er3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-er3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2b-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-a2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-a2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-er3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-er3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2r-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-a2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-a2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-er2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-er2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-er3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-er3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-et2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-et2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2v-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2w-er3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2w-er3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50\/60vg2w-et3_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50\/60vg2w-et3:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2b-en2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2b-en2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2b-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2b-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2r-en2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2r-en2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2r-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2r-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2v-en2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2v-en2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2v-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2v-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-ln25\/35\/50vg2w-en2_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-ln25\/35\/50vg2w-en2:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-rw25\/35\/50vg-e1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-rw25\/35\/50vg-e1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-rw25\/35\/50vg-er1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-rw25\/35\/50vg-er1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-rw25\/35\/50vg-et1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-rw25\/35\/50vg-et1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-rw25\/35\/50vg-sc1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-rw25\/35\/50vg-sc1:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-wx18\/20\/25vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-wx18\/20\/25vfk:-:*:*:*:*:*:*:*|cpe:2.3:o:mitsubishielectric:msz-zy09\/12\/18vfk_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:mitsubishielectric:msz-zy09\/12\/18vfk:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
         </is>
       </c>
     </row>
@@ -547,6 +566,11 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
